--- a/backend/DATA_MODEL.xlsx
+++ b/backend/DATA_MODEL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vonje\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Randel\Downloads\Von Files\Von_Thesis\Von_Thesis\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81E3904-DDC8-4CAB-AF71-91D7A1D19156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{473B333C-C641-4E66-A6A5-D9145B194DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2796" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA_MODEL" sheetId="4" r:id="rId1"/>
@@ -3436,6 +3436,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF5B3F86"/>
+          <bgColor rgb="FF5B3F86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border>
         <left style="thin">
           <color rgb="FF5B3F86"/>
@@ -3470,1736 +3494,1736 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5238,728 +5262,728 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5998,200 +6022,200 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6230,744 +6254,744 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7006,408 +7030,408 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7427,37 +7451,13 @@
         </bottom>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF5B3F86"/>
-          <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="388">
     <tableStyle name="SURVEY RESULTS-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="784"/>
-      <tableStyleElement type="headerRow" dxfId="787"/>
-      <tableStyleElement type="firstRowStripe" dxfId="786"/>
-      <tableStyleElement type="secondRowStripe" dxfId="785"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="787"/>
+      <tableStyleElement type="headerRow" dxfId="786"/>
+      <tableStyleElement type="firstRowStripe" dxfId="785"/>
+      <tableStyleElement type="secondRowStripe" dxfId="784"/>
     </tableStyle>
     <tableStyle name="2022 -2025 PRC DATA RECORD-style" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="firstRowStripe" dxfId="783"/>
@@ -7560,10 +7560,10 @@
       <tableStyleElement type="secondRowStripe" dxfId="734"/>
     </tableStyle>
     <tableStyle name="DATA_MODEL-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF1A000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="730"/>
-      <tableStyleElement type="headerRow" dxfId="733"/>
-      <tableStyleElement type="firstRowStripe" dxfId="732"/>
-      <tableStyleElement type="secondRowStripe" dxfId="731"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="733"/>
+      <tableStyleElement type="headerRow" dxfId="732"/>
+      <tableStyleElement type="firstRowStripe" dxfId="731"/>
+      <tableStyleElement type="secondRowStripe" dxfId="730"/>
     </tableStyle>
     <tableStyle name="DATA_MODEL-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF1B000000}">
       <tableStyleElement type="firstRowStripe" dxfId="729"/>
@@ -7750,10 +7750,10 @@
       <tableStyleElement type="secondRowStripe" dxfId="638"/>
     </tableStyle>
     <tableStyle name="DATA_EVALUATION-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF49000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="634"/>
-      <tableStyleElement type="headerRow" dxfId="637"/>
-      <tableStyleElement type="firstRowStripe" dxfId="636"/>
-      <tableStyleElement type="secondRowStripe" dxfId="635"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="637"/>
+      <tableStyleElement type="headerRow" dxfId="636"/>
+      <tableStyleElement type="firstRowStripe" dxfId="635"/>
+      <tableStyleElement type="secondRowStripe" dxfId="634"/>
     </tableStyle>
     <tableStyle name="DATA_EVALUATION-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF4A000000}">
       <tableStyleElement type="firstRowStripe" dxfId="633"/>
@@ -7804,10 +7804,10 @@
       <tableStyleElement type="secondRowStripe" dxfId="610"/>
     </tableStyle>
     <tableStyle name="DATA_ALL1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF56000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="606"/>
-      <tableStyleElement type="headerRow" dxfId="609"/>
-      <tableStyleElement type="firstRowStripe" dxfId="608"/>
-      <tableStyleElement type="secondRowStripe" dxfId="607"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="609"/>
+      <tableStyleElement type="headerRow" dxfId="608"/>
+      <tableStyleElement type="firstRowStripe" dxfId="607"/>
+      <tableStyleElement type="secondRowStripe" dxfId="606"/>
     </tableStyle>
     <tableStyle name="DATA_ALL1-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF57000000}">
       <tableStyleElement type="firstRowStripe" dxfId="605"/>
@@ -7990,10 +7990,10 @@
       <tableStyleElement type="secondRowStripe" dxfId="516"/>
     </tableStyle>
     <tableStyle name="DATA_DRAFT (EVALUATION)-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF84000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="512"/>
-      <tableStyleElement type="headerRow" dxfId="515"/>
-      <tableStyleElement type="firstRowStripe" dxfId="514"/>
-      <tableStyleElement type="secondRowStripe" dxfId="513"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="515"/>
+      <tableStyleElement type="headerRow" dxfId="514"/>
+      <tableStyleElement type="firstRowStripe" dxfId="513"/>
+      <tableStyleElement type="secondRowStripe" dxfId="512"/>
     </tableStyle>
     <tableStyle name="DATA_DRAFT (EVALUATION)-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF85000000}">
       <tableStyleElement type="firstRowStripe" dxfId="511"/>
@@ -8428,10 +8428,10 @@
       <tableStyleElement type="secondRowStripe" dxfId="296"/>
     </tableStyle>
     <tableStyle name="DATA_DRAFT (MODEL)-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFFF1000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="292"/>
-      <tableStyleElement type="headerRow" dxfId="295"/>
-      <tableStyleElement type="firstRowStripe" dxfId="294"/>
-      <tableStyleElement type="secondRowStripe" dxfId="293"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="295"/>
+      <tableStyleElement type="headerRow" dxfId="294"/>
+      <tableStyleElement type="firstRowStripe" dxfId="293"/>
+      <tableStyleElement type="secondRowStripe" dxfId="292"/>
     </tableStyle>
     <tableStyle name="DATA_DRAFT (MODEL)-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFFF2000000}">
       <tableStyleElement type="firstRowStripe" dxfId="291"/>
@@ -12488,23 +12488,23 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:CT124"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.6640625" customWidth="1"/>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:98" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:98" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>154</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>151</v>
@@ -12789,7 +12789,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>176</v>
       </c>
@@ -13079,7 +13079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>160</v>
       </c>
@@ -13361,7 +13361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>161</v>
       </c>
@@ -13643,7 +13643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>104</v>
       </c>
@@ -13935,7 +13935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>117</v>
       </c>
@@ -14227,7 +14227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>126</v>
       </c>
@@ -14509,7 +14509,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>175</v>
       </c>
@@ -14795,7 +14795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>261</v>
       </c>
@@ -15079,7 +15079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>186</v>
       </c>
@@ -15365,7 +15365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>189</v>
       </c>
@@ -15647,7 +15647,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>190</v>
       </c>
@@ -15931,7 +15931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>191</v>
       </c>
@@ -16219,7 +16219,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>192</v>
       </c>
@@ -16503,7 +16503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>262</v>
       </c>
@@ -16791,7 +16791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>263</v>
       </c>
@@ -17073,7 +17073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>193</v>
       </c>
@@ -17359,7 +17359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>194</v>
       </c>
@@ -17643,7 +17643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>195</v>
       </c>
@@ -17931,7 +17931,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>131</v>
       </c>
@@ -18217,7 +18217,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>136</v>
       </c>
@@ -18501,7 +18501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>140</v>
       </c>
@@ -18785,7 +18785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>142</v>
       </c>
@@ -19071,7 +19071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>197</v>
       </c>
@@ -19357,7 +19357,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>198</v>
       </c>
@@ -19645,7 +19645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>199</v>
       </c>
@@ -19933,7 +19933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>200</v>
       </c>
@@ -20221,7 +20221,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>201</v>
       </c>
@@ -20505,7 +20505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>202</v>
       </c>
@@ -20791,7 +20791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>203</v>
       </c>
@@ -21081,7 +21081,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>206</v>
       </c>
@@ -21365,7 +21365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>212</v>
       </c>
@@ -21651,7 +21651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>214</v>
       </c>
@@ -21935,7 +21935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>215</v>
       </c>
@@ -22219,7 +22219,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>216</v>
       </c>
@@ -22503,7 +22503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>217</v>
       </c>
@@ -22793,7 +22793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>220</v>
       </c>
@@ -23075,7 +23075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>221</v>
       </c>
@@ -23361,7 +23361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>265</v>
       </c>
@@ -23645,7 +23645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>226</v>
       </c>
@@ -23935,7 +23935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>230</v>
       </c>
@@ -24219,7 +24219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>231</v>
       </c>
@@ -24503,7 +24503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>232</v>
       </c>
@@ -24791,7 +24791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>233</v>
       </c>
@@ -25073,7 +25073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>234</v>
       </c>
@@ -25357,7 +25357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>244</v>
       </c>
@@ -25651,7 +25651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>267</v>
       </c>
@@ -25941,7 +25941,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
         <v>268</v>
       </c>
@@ -26235,7 +26235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>197</v>
       </c>
@@ -26521,7 +26521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
         <v>196</v>
       </c>
@@ -26809,7 +26809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
         <v>269</v>
       </c>
@@ -27099,7 +27099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
         <v>148</v>
       </c>
@@ -27387,7 +27387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
         <v>270</v>
       </c>
@@ -27673,7 +27673,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
         <v>271</v>
       </c>
@@ -27965,7 +27965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>245</v>
       </c>
@@ -28251,7 +28251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>272</v>
       </c>
@@ -28541,7 +28541,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>271</v>
       </c>
@@ -28829,7 +28829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
         <v>241</v>
       </c>
@@ -29117,7 +29117,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
         <v>247</v>
       </c>
@@ -29403,7 +29403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
         <v>253</v>
       </c>
@@ -29685,7 +29685,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
         <v>254</v>
       </c>
@@ -29971,7 +29971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
         <v>255</v>
       </c>
@@ -30261,7 +30261,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
         <v>256</v>
       </c>
@@ -30547,7 +30547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
         <v>204</v>
       </c>
@@ -30831,7 +30831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
         <v>205</v>
       </c>
@@ -31115,7 +31115,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
         <v>274</v>
       </c>
@@ -31399,7 +31399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
         <v>208</v>
       </c>
@@ -31681,7 +31681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
         <v>210</v>
       </c>
@@ -31963,7 +31963,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A69" s="11" t="s">
         <v>211</v>
       </c>
@@ -32247,7 +32247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
         <v>213</v>
       </c>
@@ -32531,7 +32531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
         <v>236</v>
       </c>
@@ -32815,7 +32815,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A72" s="11" t="s">
         <v>245</v>
       </c>
@@ -33105,7 +33105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
         <v>237</v>
       </c>
@@ -33387,7 +33387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
         <v>239</v>
       </c>
@@ -33669,7 +33669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
         <v>235</v>
       </c>
@@ -33951,7 +33951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
         <v>222</v>
       </c>
@@ -34237,7 +34237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
         <v>246</v>
       </c>
@@ -34519,7 +34519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A78" s="11" t="s">
         <v>276</v>
       </c>
@@ -34803,7 +34803,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
         <v>248</v>
       </c>
@@ -35085,7 +35085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
         <v>249</v>
       </c>
@@ -35367,7 +35367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
         <v>277</v>
       </c>
@@ -35651,7 +35651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
         <v>250</v>
       </c>
@@ -35941,7 +35941,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A83" s="11" t="s">
         <v>251</v>
       </c>
@@ -36225,7 +36225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
         <v>252</v>
       </c>
@@ -36517,7 +36517,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
         <v>187</v>
       </c>
@@ -36805,7 +36805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
         <v>188</v>
       </c>
@@ -37091,7 +37091,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
         <v>223</v>
       </c>
@@ -37373,7 +37373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
         <v>224</v>
       </c>
@@ -37655,7 +37655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A89" s="11" t="s">
         <v>282</v>
       </c>
@@ -37939,7 +37939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
         <v>225</v>
       </c>
@@ -38221,7 +38221,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
         <v>240</v>
       </c>
@@ -38503,7 +38503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
         <v>227</v>
       </c>
@@ -38785,7 +38785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
         <v>228</v>
       </c>
@@ -39071,7 +39071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
         <v>229</v>
       </c>
@@ -39353,7 +39353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
         <v>238</v>
       </c>
@@ -39635,7 +39635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
         <v>283</v>
       </c>
@@ -39917,7 +39917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
         <v>162</v>
       </c>
@@ -40211,7 +40211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A98" s="11" t="s">
         <v>163</v>
       </c>
@@ -40495,7 +40495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
         <v>164</v>
       </c>
@@ -40777,7 +40777,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A100" s="11" t="s">
         <v>165</v>
       </c>
@@ -41059,7 +41059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A101" s="11" t="s">
         <v>166</v>
       </c>
@@ -41353,7 +41353,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A102" s="11" t="s">
         <v>167</v>
       </c>
@@ -41635,7 +41635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
         <v>168</v>
       </c>
@@ -41917,7 +41917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A104" s="11" t="s">
         <v>218</v>
       </c>
@@ -42201,7 +42201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
         <v>177</v>
       </c>
@@ -42487,7 +42487,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
         <v>178</v>
       </c>
@@ -42771,7 +42771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
         <v>179</v>
       </c>
@@ -43055,7 +43055,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A108" s="11" t="s">
         <v>180</v>
       </c>
@@ -43339,7 +43339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
         <v>181</v>
       </c>
@@ -43633,7 +43633,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
         <v>182</v>
       </c>
@@ -43917,7 +43917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
         <v>183</v>
       </c>
@@ -44205,7 +44205,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A112" s="11" t="s">
         <v>184</v>
       </c>
@@ -44489,7 +44489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
         <v>185</v>
       </c>
@@ -44775,7 +44775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
         <v>219</v>
       </c>
@@ -45057,7 +45057,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
         <v>207</v>
       </c>
@@ -45339,7 +45339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A116" s="11" t="s">
         <v>290</v>
       </c>
@@ -45621,7 +45621,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
         <v>209</v>
       </c>
@@ -45903,7 +45903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
         <v>242</v>
       </c>
@@ -46189,7 +46189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
         <v>243</v>
       </c>
@@ -46473,7 +46473,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
         <v>170</v>
       </c>
@@ -46757,7 +46757,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
         <v>171</v>
       </c>
@@ -47043,7 +47043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
         <v>172</v>
       </c>
@@ -47325,7 +47325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A123" s="11" t="s">
         <v>173</v>
       </c>
@@ -47611,7 +47611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:98" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:98" ht="15" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
         <v>174</v>
       </c>

--- a/backend/DATA_MODEL.xlsx
+++ b/backend/DATA_MODEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Randel\Downloads\Von Files\Von_Thesis\Von_Thesis\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{473B333C-C641-4E66-A6A5-D9145B194DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB52531-58A1-45BD-B442-2C4649D61386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="DATA_MODEL" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -12498,13 +12499,13 @@
         <v>154</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>151</v>

--- a/backend/DATA_MODEL.xlsx
+++ b/backend/DATA_MODEL.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Randel\Downloads\Von Files\Von_Thesis\Von_Thesis\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB52531-58A1-45BD-B442-2C4649D61386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FCC48F0-A872-40C6-82D6-A688C3D7788B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5265" yWindow="3195" windowWidth="22845" windowHeight="12285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA_MODEL" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -12499,13 +12498,13 @@
         <v>154</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>151</v>
